--- a/01_企画/【ガント】PAW！.xlsx
+++ b/01_企画/【ガント】PAW！.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\suire\OneDrive\デスクトップ\【就職作品】PAW！\01_企画\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2416009\Project\PAW\01_企画\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8531291-44F6-481A-BC49-DC1FE3D7CEE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B56891D8-CF55-45CC-AB6B-436E17CCFC46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="スケジュール" sheetId="7" r:id="rId1"/>
@@ -39,6 +39,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -1586,6 +1589,15 @@
     <xf numFmtId="0" fontId="5" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1599,12 +1611,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1628,14 +1634,11 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="115">
+  <dxfs count="100">
     <dxf>
       <fill>
         <patternFill>
@@ -1654,195 +1657,6 @@
       <fill>
         <patternFill>
           <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2017,7 +1831,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor indexed="22"/>
+          <bgColor indexed="41"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2031,7 +1845,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor indexed="41"/>
+          <bgColor indexed="22"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2122,7 +1936,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor indexed="22"/>
+          <bgColor indexed="41"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2136,28 +1950,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2185,7 +1978,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor indexed="22"/>
+          <bgColor indexed="41"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2199,7 +1992,133 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="22"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2324,48 +2243,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
@@ -2423,6 +2300,27 @@
       <fill>
         <patternFill>
           <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2827,11 +2725,11 @@
       <c r="G2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="H2" s="60">
+      <c r="H2" s="61">
         <v>46279</v>
       </c>
-      <c r="I2" s="61"/>
-      <c r="J2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="63"/>
       <c r="K2" s="40">
         <v>1</v>
       </c>
@@ -2839,10 +2737,10 @@
         <v>2</v>
       </c>
       <c r="O2" s="31"/>
-      <c r="R2" s="59"/>
-      <c r="S2" s="59"/>
-      <c r="T2" s="59"/>
-      <c r="U2" s="59"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="60"/>
+      <c r="T2" s="60"/>
+      <c r="U2" s="60"/>
       <c r="X2" s="24"/>
       <c r="AB2" s="24"/>
       <c r="AC2" s="24"/>
@@ -5838,11 +5736,11 @@
       <c r="H6" s="35"/>
       <c r="I6" s="35"/>
       <c r="J6" s="35"/>
-      <c r="K6" s="65" t="s">
+      <c r="K6" s="66" t="s">
         <v>8</v>
       </c>
-      <c r="L6" s="55"/>
-      <c r="M6" s="56"/>
+      <c r="L6" s="58"/>
+      <c r="M6" s="59"/>
       <c r="N6" s="35"/>
       <c r="O6" s="35" t="s">
         <v>9</v>
@@ -5891,7 +5789,7 @@
       </c>
       <c r="AV6" s="35"/>
       <c r="AW6" s="35"/>
-      <c r="AX6" s="66" t="s">
+      <c r="AX6" s="52" t="s">
         <v>81</v>
       </c>
       <c r="AY6" s="35"/>
@@ -5970,24 +5868,24 @@
       <c r="DD6" s="35"/>
       <c r="DE6" s="35"/>
       <c r="DF6" s="35"/>
-      <c r="DG6" s="52" t="s">
+      <c r="DG6" s="55" t="s">
         <v>24</v>
       </c>
-      <c r="DH6" s="55"/>
-      <c r="DI6" s="55"/>
-      <c r="DJ6" s="55"/>
-      <c r="DK6" s="55"/>
-      <c r="DL6" s="55"/>
-      <c r="DM6" s="55"/>
-      <c r="DN6" s="55"/>
-      <c r="DO6" s="55"/>
-      <c r="DP6" s="55"/>
-      <c r="DQ6" s="55"/>
-      <c r="DR6" s="55"/>
-      <c r="DS6" s="55"/>
-      <c r="DT6" s="55"/>
-      <c r="DU6" s="55"/>
-      <c r="DV6" s="56"/>
+      <c r="DH6" s="58"/>
+      <c r="DI6" s="58"/>
+      <c r="DJ6" s="58"/>
+      <c r="DK6" s="58"/>
+      <c r="DL6" s="58"/>
+      <c r="DM6" s="58"/>
+      <c r="DN6" s="58"/>
+      <c r="DO6" s="58"/>
+      <c r="DP6" s="58"/>
+      <c r="DQ6" s="58"/>
+      <c r="DR6" s="58"/>
+      <c r="DS6" s="58"/>
+      <c r="DT6" s="58"/>
+      <c r="DU6" s="58"/>
+      <c r="DV6" s="59"/>
       <c r="DW6" s="36" t="s">
         <v>25</v>
       </c>
@@ -6021,11 +5919,11 @@
       <c r="ES6" s="35"/>
       <c r="ET6" s="35"/>
       <c r="EU6" s="35"/>
-      <c r="EV6" s="52" t="s">
+      <c r="EV6" s="55" t="s">
         <v>28</v>
       </c>
-      <c r="EW6" s="53"/>
-      <c r="EX6" s="54"/>
+      <c r="EW6" s="56"/>
+      <c r="EX6" s="57"/>
       <c r="EY6" s="36" t="s">
         <v>29</v>
       </c>
@@ -6678,11 +6576,11 @@
       </c>
     </row>
     <row r="8" spans="1:251" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A8" s="63" t="s">
+      <c r="A8" s="64" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="64"/>
-      <c r="C8" s="64"/>
+      <c r="B8" s="65"/>
+      <c r="C8" s="65"/>
       <c r="D8" s="38"/>
       <c r="E8" s="38"/>
       <c r="F8" s="38"/>
@@ -10756,11 +10654,11 @@
       </c>
     </row>
     <row r="16" spans="1:251" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A16" s="57" t="s">
+      <c r="A16" s="53" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="58"/>
-      <c r="C16" s="58"/>
+      <c r="B16" s="54"/>
+      <c r="C16" s="54"/>
       <c r="D16" s="39"/>
       <c r="E16" s="39"/>
       <c r="F16" s="39"/>
@@ -11315,7 +11213,9 @@
       <c r="F17" s="17">
         <v>46281</v>
       </c>
-      <c r="G17" s="17"/>
+      <c r="G17" s="17">
+        <v>46283</v>
+      </c>
       <c r="H17" s="18" t="str">
         <f t="shared" ca="1" si="22"/>
         <v/>
@@ -11334,7 +11234,7 @@
       </c>
       <c r="L17" s="28" t="str">
         <f t="shared" ca="1" si="22"/>
-        <v/>
+        <v>→</v>
       </c>
       <c r="M17" s="18" t="str">
         <f t="shared" ca="1" si="22"/>
@@ -12417,7 +12317,9 @@
       <c r="F19" s="17">
         <v>46293</v>
       </c>
-      <c r="G19" s="17"/>
+      <c r="G19" s="17">
+        <v>46289</v>
+      </c>
       <c r="H19" s="18" t="str">
         <f t="shared" ca="1" si="22"/>
         <v/>
@@ -12460,7 +12362,7 @@
       </c>
       <c r="R19" s="43" t="str">
         <f t="shared" ca="1" si="23"/>
-        <v/>
+        <v>→</v>
       </c>
       <c r="S19" s="18" t="str">
         <f t="shared" ca="1" si="23"/>
@@ -23922,11 +23824,11 @@
       </c>
     </row>
     <row r="40" spans="1:251" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.15">
-      <c r="A40" s="57" t="s">
+      <c r="A40" s="53" t="s">
         <v>76</v>
       </c>
-      <c r="B40" s="58"/>
-      <c r="C40" s="58"/>
+      <c r="B40" s="54"/>
+      <c r="C40" s="54"/>
       <c r="D40" s="17"/>
       <c r="E40" s="17"/>
       <c r="F40" s="17"/>
@@ -57489,281 +57391,281 @@
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="A36:A39">
-    <cfRule type="expression" dxfId="114" priority="736" stopIfTrue="1">
+    <cfRule type="expression" dxfId="99" priority="736" stopIfTrue="1">
       <formula>OR(AND(ISBLANK($E35)=TRUE,ISBLANK($D35)=FALSE,$D35&lt;=TODAY()),AND(ISBLANK($G35)=TRUE,ISBLANK($F35)=FALSE,$F35&lt;TODAY()))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="113" priority="735" stopIfTrue="1">
+    <cfRule type="expression" dxfId="98" priority="735" stopIfTrue="1">
       <formula>ISBLANK($G35)=FALSE</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="112" priority="737" stopIfTrue="1">
+    <cfRule type="expression" dxfId="97" priority="737" stopIfTrue="1">
       <formula>AND(ISBLANK($D35)=FALSE,ISBLANK($E35)=FALSE,$E35&lt;=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A7:G7 A8 A9:G15 A16 A44:G101 D25:F27 A24:A28 C30:G30 A43:F43 C42:F43 A27:G29 G38:G43 G31:G35 A35:F35 A30:A36 A36:G37 A17:G23 D24:G26 D31:F32 C32:F35 A37:F39 A40 A42:A43 D40:F41 A41:F41">
-    <cfRule type="expression" dxfId="56" priority="192" stopIfTrue="1">
+    <cfRule type="expression" dxfId="96" priority="192" stopIfTrue="1">
       <formula>AND(ISBLANK($D7)=FALSE,ISBLANK($E7)=FALSE,$E7&lt;=TODAY())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="55" priority="191" stopIfTrue="1">
+    <cfRule type="expression" dxfId="95" priority="191" stopIfTrue="1">
       <formula>OR(AND(ISBLANK($E7)=TRUE,ISBLANK($D7)=FALSE,$D7&lt;=TODAY()),AND(ISBLANK($G7)=TRUE,ISBLANK($F7)=FALSE,$F7&lt;TODAY()))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A7:G7 A8 A9:G15 A16 A44:G101 D25:F27 A24:A28 C30:G30 A43:F43 C42:F43 A27:G29 G38:G43 G31:G35 A35:F35 A30:A36 A36:G37 A17:G23 D24:G26 D31:F32 C32:F35 A37:F39 A40 A42:A43 D40:F41 A41:F41">
-    <cfRule type="expression" dxfId="54" priority="190" stopIfTrue="1">
+    <cfRule type="expression" dxfId="94" priority="190" stopIfTrue="1">
       <formula>ISBLANK($G7)=FALSE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28 B30">
-    <cfRule type="expression" dxfId="111" priority="91" stopIfTrue="1">
+    <cfRule type="expression" dxfId="93" priority="91" stopIfTrue="1">
       <formula>ISBLANK($G24)=FALSE</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="110" priority="92" stopIfTrue="1">
+    <cfRule type="expression" dxfId="92" priority="92" stopIfTrue="1">
       <formula>OR(AND(ISBLANK($E24)=TRUE,ISBLANK($D24)=FALSE,$D24&lt;=TODAY()),AND(ISBLANK($G24)=TRUE,ISBLANK($F24)=FALSE,$F24&lt;TODAY()))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="109" priority="93" stopIfTrue="1">
+    <cfRule type="expression" dxfId="91" priority="93" stopIfTrue="1">
       <formula>AND(ISBLANK($D24)=FALSE,ISBLANK($E24)=FALSE,$E24&lt;=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36:B39">
-    <cfRule type="expression" dxfId="108" priority="76" stopIfTrue="1">
+    <cfRule type="expression" dxfId="90" priority="76" stopIfTrue="1">
       <formula>ISBLANK($G36)=FALSE</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="107" priority="77" stopIfTrue="1">
+    <cfRule type="expression" dxfId="89" priority="77" stopIfTrue="1">
       <formula>OR(AND(ISBLANK($E36)=TRUE,ISBLANK($D36)=FALSE,$D36&lt;=TODAY()),AND(ISBLANK($G36)=TRUE,ISBLANK($F36)=FALSE,$F36&lt;TODAY()))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="106" priority="78" stopIfTrue="1">
+    <cfRule type="expression" dxfId="88" priority="78" stopIfTrue="1">
       <formula>AND(ISBLANK($D36)=FALSE,ISBLANK($E36)=FALSE,$E36&lt;=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B24:C27">
-    <cfRule type="expression" dxfId="105" priority="102" stopIfTrue="1">
+    <cfRule type="expression" dxfId="87" priority="102" stopIfTrue="1">
       <formula>AND(ISBLANK($D20)=FALSE,ISBLANK($E20)=FALSE,$E20&lt;=TODAY())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="104" priority="100" stopIfTrue="1">
+    <cfRule type="expression" dxfId="86" priority="100" stopIfTrue="1">
       <formula>ISBLANK($G20)=FALSE</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="103" priority="101" stopIfTrue="1">
+    <cfRule type="expression" dxfId="85" priority="101" stopIfTrue="1">
       <formula>OR(AND(ISBLANK($E20)=TRUE,ISBLANK($D20)=FALSE,$D20&lt;=TODAY()),AND(ISBLANK($G20)=TRUE,ISBLANK($F20)=FALSE,$F20&lt;TODAY()))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36:C36">
-    <cfRule type="expression" dxfId="102" priority="117" stopIfTrue="1">
+    <cfRule type="expression" dxfId="84" priority="117" stopIfTrue="1">
       <formula>AND(ISBLANK($D24)=FALSE,ISBLANK($E24)=FALSE,$E24&lt;=TODAY())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="101" priority="116" stopIfTrue="1">
+    <cfRule type="expression" dxfId="83" priority="116" stopIfTrue="1">
       <formula>OR(AND(ISBLANK($E24)=TRUE,ISBLANK($D24)=FALSE,$D24&lt;=TODAY()),AND(ISBLANK($G24)=TRUE,ISBLANK($F24)=FALSE,$F24&lt;TODAY()))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="100" priority="115" stopIfTrue="1">
+    <cfRule type="expression" dxfId="82" priority="115" stopIfTrue="1">
       <formula>ISBLANK($G24)=FALSE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28 C30">
-    <cfRule type="expression" dxfId="93" priority="90" stopIfTrue="1">
+    <cfRule type="expression" dxfId="81" priority="90" stopIfTrue="1">
       <formula>AND(ISBLANK($D24)=FALSE,ISBLANK($E24)=FALSE,$E24&lt;=TODAY())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="92" priority="89" stopIfTrue="1">
+    <cfRule type="expression" dxfId="80" priority="89" stopIfTrue="1">
       <formula>OR(AND(ISBLANK($E24)=TRUE,ISBLANK($D24)=FALSE,$D24&lt;=TODAY()),AND(ISBLANK($G24)=TRUE,ISBLANK($F24)=FALSE,$F24&lt;TODAY()))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="91" priority="88" stopIfTrue="1">
+    <cfRule type="expression" dxfId="79" priority="88" stopIfTrue="1">
       <formula>ISBLANK($G24)=FALSE</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C36:C39">
-    <cfRule type="expression" dxfId="90" priority="96" stopIfTrue="1">
+    <cfRule type="expression" dxfId="78" priority="96" stopIfTrue="1">
       <formula>AND(ISBLANK($D32)=FALSE,ISBLANK($E32)=FALSE,$E32&lt;=TODAY())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="89" priority="94" stopIfTrue="1">
+    <cfRule type="expression" dxfId="77" priority="94" stopIfTrue="1">
       <formula>ISBLANK($G32)=FALSE</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="88" priority="95" stopIfTrue="1">
+    <cfRule type="expression" dxfId="76" priority="95" stopIfTrue="1">
       <formula>OR(AND(ISBLANK($E32)=TRUE,ISBLANK($D32)=FALSE,$D32&lt;=TODAY()),AND(ISBLANK($G32)=TRUE,ISBLANK($F32)=FALSE,$F32&lt;TODAY()))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:IQ3">
-    <cfRule type="expression" dxfId="87" priority="719" stopIfTrue="1">
+    <cfRule type="expression" dxfId="75" priority="719" stopIfTrue="1">
       <formula>AND(DAY(H4)&gt;=1,DAY(H4)&lt;=$K$2)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:IQ5">
-    <cfRule type="expression" dxfId="86" priority="720" stopIfTrue="1">
+    <cfRule type="expression" dxfId="74" priority="720" stopIfTrue="1">
       <formula>AND(H$4&lt;=TODAY(),H$4+$K$2-1&gt;=TODAY())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="85" priority="722" stopIfTrue="1">
+    <cfRule type="expression" dxfId="73" priority="722" stopIfTrue="1">
       <formula>WEEKDAY(H$4)=7</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="84" priority="721" stopIfTrue="1">
+    <cfRule type="expression" dxfId="72" priority="721" stopIfTrue="1">
       <formula>WEEKDAY(H$4)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H7:IQ101">
-    <cfRule type="expression" dxfId="83" priority="723" stopIfTrue="1">
+    <cfRule type="expression" dxfId="71" priority="723" stopIfTrue="1">
       <formula>OR(AND($D7&gt;=H$4,$D7&lt;=H$4+$K$2-1),AND($F7&gt;=H$4,$F7&lt;=H$4+$K$2-1),AND($D7&lt;H$4,$F7&gt;H$4+$K$2-1))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="82" priority="724" stopIfTrue="1">
+    <cfRule type="expression" dxfId="70" priority="724" stopIfTrue="1">
       <formula>WEEKDAY(H$4)=1</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="81" priority="725" stopIfTrue="1">
+    <cfRule type="expression" dxfId="69" priority="725" stopIfTrue="1">
       <formula>WEEKDAY(H$4)=7</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B42:B43">
-    <cfRule type="expression" dxfId="77" priority="70" stopIfTrue="1">
+    <cfRule type="expression" dxfId="68" priority="70" stopIfTrue="1">
       <formula>ISBLANK($G38)=FALSE</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="76" priority="71" stopIfTrue="1">
+    <cfRule type="expression" dxfId="67" priority="71" stopIfTrue="1">
       <formula>OR(AND(ISBLANK($E38)=TRUE,ISBLANK($D38)=FALSE,$D38&lt;=TODAY()),AND(ISBLANK($G38)=TRUE,ISBLANK($F38)=FALSE,$F38&lt;TODAY()))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="75" priority="72" stopIfTrue="1">
+    <cfRule type="expression" dxfId="66" priority="72" stopIfTrue="1">
       <formula>AND(ISBLANK($D38)=FALSE,ISBLANK($E38)=FALSE,$E38&lt;=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37:C37">
-    <cfRule type="expression" dxfId="69" priority="64" stopIfTrue="1">
+    <cfRule type="expression" dxfId="65" priority="64" stopIfTrue="1">
       <formula>ISBLANK($G25)=FALSE</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="70" priority="65" stopIfTrue="1">
+    <cfRule type="expression" dxfId="64" priority="65" stopIfTrue="1">
       <formula>OR(AND(ISBLANK($E25)=TRUE,ISBLANK($D25)=FALSE,$D25&lt;=TODAY()),AND(ISBLANK($G25)=TRUE,ISBLANK($F25)=FALSE,$F25&lt;TODAY()))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="71" priority="66" stopIfTrue="1">
+    <cfRule type="expression" dxfId="63" priority="66" stopIfTrue="1">
       <formula>AND(ISBLANK($D25)=FALSE,ISBLANK($E25)=FALSE,$E25&lt;=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38:C38">
-    <cfRule type="expression" dxfId="68" priority="61" stopIfTrue="1">
+    <cfRule type="expression" dxfId="62" priority="61" stopIfTrue="1">
       <formula>ISBLANK($G26)=FALSE</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="67" priority="62" stopIfTrue="1">
+    <cfRule type="expression" dxfId="61" priority="62" stopIfTrue="1">
       <formula>OR(AND(ISBLANK($E26)=TRUE,ISBLANK($D26)=FALSE,$D26&lt;=TODAY()),AND(ISBLANK($G26)=TRUE,ISBLANK($F26)=FALSE,$F26&lt;TODAY()))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="66" priority="63" stopIfTrue="1">
+    <cfRule type="expression" dxfId="60" priority="63" stopIfTrue="1">
       <formula>AND(ISBLANK($D26)=FALSE,ISBLANK($E26)=FALSE,$E26&lt;=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B31:B36">
-    <cfRule type="expression" dxfId="65" priority="58" stopIfTrue="1">
+    <cfRule type="expression" dxfId="59" priority="58" stopIfTrue="1">
       <formula>ISBLANK($G27)=FALSE</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="64" priority="59" stopIfTrue="1">
+    <cfRule type="expression" dxfId="58" priority="59" stopIfTrue="1">
       <formula>OR(AND(ISBLANK($E27)=TRUE,ISBLANK($D27)=FALSE,$D27&lt;=TODAY()),AND(ISBLANK($G27)=TRUE,ISBLANK($F27)=FALSE,$F27&lt;TODAY()))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="63" priority="60" stopIfTrue="1">
+    <cfRule type="expression" dxfId="57" priority="60" stopIfTrue="1">
       <formula>AND(ISBLANK($D27)=FALSE,ISBLANK($E27)=FALSE,$E27&lt;=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C31:C32">
-    <cfRule type="expression" dxfId="62" priority="55" stopIfTrue="1">
+    <cfRule type="expression" dxfId="56" priority="55" stopIfTrue="1">
       <formula>ISBLANK($G27)=FALSE</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="61" priority="56" stopIfTrue="1">
+    <cfRule type="expression" dxfId="55" priority="56" stopIfTrue="1">
       <formula>OR(AND(ISBLANK($E27)=TRUE,ISBLANK($D27)=FALSE,$D27&lt;=TODAY()),AND(ISBLANK($G27)=TRUE,ISBLANK($F27)=FALSE,$F27&lt;TODAY()))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="60" priority="57" stopIfTrue="1">
+    <cfRule type="expression" dxfId="54" priority="57" stopIfTrue="1">
       <formula>AND(ISBLANK($D27)=FALSE,ISBLANK($E27)=FALSE,$E27&lt;=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B37:C37">
-    <cfRule type="expression" dxfId="59" priority="52" stopIfTrue="1">
+    <cfRule type="expression" dxfId="53" priority="52" stopIfTrue="1">
       <formula>ISBLANK($G25)=FALSE</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="58" priority="53" stopIfTrue="1">
+    <cfRule type="expression" dxfId="52" priority="53" stopIfTrue="1">
       <formula>OR(AND(ISBLANK($E25)=TRUE,ISBLANK($D25)=FALSE,$D25&lt;=TODAY()),AND(ISBLANK($G25)=TRUE,ISBLANK($F25)=FALSE,$F25&lt;TODAY()))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="57" priority="54" stopIfTrue="1">
+    <cfRule type="expression" dxfId="51" priority="54" stopIfTrue="1">
       <formula>AND(ISBLANK($D25)=FALSE,ISBLANK($E25)=FALSE,$E25&lt;=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38:C38">
-    <cfRule type="expression" dxfId="53" priority="49" stopIfTrue="1">
+    <cfRule type="expression" dxfId="50" priority="49" stopIfTrue="1">
       <formula>ISBLANK($G26)=FALSE</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="50" stopIfTrue="1">
+    <cfRule type="expression" dxfId="49" priority="50" stopIfTrue="1">
       <formula>OR(AND(ISBLANK($E26)=TRUE,ISBLANK($D26)=FALSE,$D26&lt;=TODAY()),AND(ISBLANK($G26)=TRUE,ISBLANK($F26)=FALSE,$F26&lt;TODAY()))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="51" priority="51" stopIfTrue="1">
+    <cfRule type="expression" dxfId="48" priority="51" stopIfTrue="1">
       <formula>AND(ISBLANK($D26)=FALSE,ISBLANK($E26)=FALSE,$E26&lt;=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38:C38">
-    <cfRule type="expression" dxfId="50" priority="46" stopIfTrue="1">
+    <cfRule type="expression" dxfId="47" priority="46" stopIfTrue="1">
       <formula>ISBLANK($G26)=FALSE</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="49" priority="47" stopIfTrue="1">
+    <cfRule type="expression" dxfId="46" priority="47" stopIfTrue="1">
       <formula>OR(AND(ISBLANK($E26)=TRUE,ISBLANK($D26)=FALSE,$D26&lt;=TODAY()),AND(ISBLANK($G26)=TRUE,ISBLANK($F26)=FALSE,$F26&lt;TODAY()))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="48" priority="48" stopIfTrue="1">
+    <cfRule type="expression" dxfId="45" priority="48" stopIfTrue="1">
       <formula>AND(ISBLANK($D26)=FALSE,ISBLANK($E26)=FALSE,$E26&lt;=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B39:C39">
-    <cfRule type="expression" dxfId="47" priority="43" stopIfTrue="1">
+    <cfRule type="expression" dxfId="44" priority="43" stopIfTrue="1">
       <formula>ISBLANK($G27)=FALSE</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="46" priority="44" stopIfTrue="1">
+    <cfRule type="expression" dxfId="43" priority="44" stopIfTrue="1">
       <formula>OR(AND(ISBLANK($E27)=TRUE,ISBLANK($D27)=FALSE,$D27&lt;=TODAY()),AND(ISBLANK($G27)=TRUE,ISBLANK($F27)=FALSE,$F27&lt;TODAY()))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="45" priority="45" stopIfTrue="1">
+    <cfRule type="expression" dxfId="42" priority="45" stopIfTrue="1">
       <formula>AND(ISBLANK($D27)=FALSE,ISBLANK($E27)=FALSE,$E27&lt;=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B39:C39">
-    <cfRule type="expression" dxfId="44" priority="40" stopIfTrue="1">
+    <cfRule type="expression" dxfId="41" priority="40" stopIfTrue="1">
       <formula>ISBLANK($G27)=FALSE</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="43" priority="41" stopIfTrue="1">
+    <cfRule type="expression" dxfId="40" priority="41" stopIfTrue="1">
       <formula>OR(AND(ISBLANK($E27)=TRUE,ISBLANK($D27)=FALSE,$D27&lt;=TODAY()),AND(ISBLANK($G27)=TRUE,ISBLANK($F27)=FALSE,$F27&lt;TODAY()))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="42" priority="42" stopIfTrue="1">
+    <cfRule type="expression" dxfId="39" priority="42" stopIfTrue="1">
       <formula>AND(ISBLANK($D27)=FALSE,ISBLANK($E27)=FALSE,$E27&lt;=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B39:C39">
-    <cfRule type="expression" dxfId="41" priority="37" stopIfTrue="1">
+    <cfRule type="expression" dxfId="38" priority="37" stopIfTrue="1">
       <formula>ISBLANK($G27)=FALSE</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="38" stopIfTrue="1">
+    <cfRule type="expression" dxfId="37" priority="38" stopIfTrue="1">
       <formula>OR(AND(ISBLANK($E27)=TRUE,ISBLANK($D27)=FALSE,$D27&lt;=TODAY()),AND(ISBLANK($G27)=TRUE,ISBLANK($F27)=FALSE,$F27&lt;TODAY()))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="39" priority="39" stopIfTrue="1">
+    <cfRule type="expression" dxfId="36" priority="39" stopIfTrue="1">
       <formula>AND(ISBLANK($D27)=FALSE,ISBLANK($E27)=FALSE,$E27&lt;=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38:C38">
-    <cfRule type="expression" dxfId="38" priority="34" stopIfTrue="1">
+    <cfRule type="expression" dxfId="35" priority="34" stopIfTrue="1">
       <formula>ISBLANK($G26)=FALSE</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="35" stopIfTrue="1">
+    <cfRule type="expression" dxfId="34" priority="35" stopIfTrue="1">
       <formula>OR(AND(ISBLANK($E26)=TRUE,ISBLANK($D26)=FALSE,$D26&lt;=TODAY()),AND(ISBLANK($G26)=TRUE,ISBLANK($F26)=FALSE,$F26&lt;TODAY()))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="36" stopIfTrue="1">
+    <cfRule type="expression" dxfId="33" priority="36" stopIfTrue="1">
       <formula>AND(ISBLANK($D26)=FALSE,ISBLANK($E26)=FALSE,$E26&lt;=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38:C38">
-    <cfRule type="expression" dxfId="35" priority="31" stopIfTrue="1">
+    <cfRule type="expression" dxfId="32" priority="31" stopIfTrue="1">
       <formula>ISBLANK($G26)=FALSE</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="34" priority="32" stopIfTrue="1">
+    <cfRule type="expression" dxfId="31" priority="32" stopIfTrue="1">
       <formula>OR(AND(ISBLANK($E26)=TRUE,ISBLANK($D26)=FALSE,$D26&lt;=TODAY()),AND(ISBLANK($G26)=TRUE,ISBLANK($F26)=FALSE,$F26&lt;TODAY()))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="33" priority="33" stopIfTrue="1">
+    <cfRule type="expression" dxfId="30" priority="33" stopIfTrue="1">
       <formula>AND(ISBLANK($D26)=FALSE,ISBLANK($E26)=FALSE,$E26&lt;=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B38:C38">
-    <cfRule type="expression" dxfId="32" priority="28" stopIfTrue="1">
+    <cfRule type="expression" dxfId="29" priority="28" stopIfTrue="1">
       <formula>ISBLANK($G26)=FALSE</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="31" priority="29" stopIfTrue="1">
+    <cfRule type="expression" dxfId="28" priority="29" stopIfTrue="1">
       <formula>OR(AND(ISBLANK($E26)=TRUE,ISBLANK($D26)=FALSE,$D26&lt;=TODAY()),AND(ISBLANK($G26)=TRUE,ISBLANK($F26)=FALSE,$F26&lt;TODAY()))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="30" stopIfTrue="1">
+    <cfRule type="expression" dxfId="27" priority="30" stopIfTrue="1">
       <formula>AND(ISBLANK($D26)=FALSE,ISBLANK($E26)=FALSE,$E26&lt;=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A41">
-    <cfRule type="expression" dxfId="25" priority="25" stopIfTrue="1">
+    <cfRule type="expression" dxfId="26" priority="25" stopIfTrue="1">
       <formula>ISBLANK($G40)=FALSE</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="26" stopIfTrue="1">
+    <cfRule type="expression" dxfId="25" priority="26" stopIfTrue="1">
       <formula>OR(AND(ISBLANK($E40)=TRUE,ISBLANK($D40)=FALSE,$D40&lt;=TODAY()),AND(ISBLANK($G40)=TRUE,ISBLANK($F40)=FALSE,$F40&lt;TODAY()))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="24" priority="27" stopIfTrue="1">
@@ -57782,13 +57684,13 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C41">
-    <cfRule type="expression" dxfId="19" priority="22" stopIfTrue="1">
+    <cfRule type="expression" dxfId="20" priority="22" stopIfTrue="1">
       <formula>ISBLANK($G37)=FALSE</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="23" stopIfTrue="1">
+    <cfRule type="expression" dxfId="19" priority="23" stopIfTrue="1">
       <formula>OR(AND(ISBLANK($E37)=TRUE,ISBLANK($D37)=FALSE,$D37&lt;=TODAY()),AND(ISBLANK($G37)=TRUE,ISBLANK($F37)=FALSE,$F37&lt;TODAY()))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="24" stopIfTrue="1">
+    <cfRule type="expression" dxfId="18" priority="24" stopIfTrue="1">
       <formula>AND(ISBLANK($D37)=FALSE,ISBLANK($E37)=FALSE,$E37&lt;=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
@@ -57877,15 +57779,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_x5b9f__x88c5_ xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">false</_x5b9f__x88c5_>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -58156,21 +58055,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_x5b9f__x88c5_ xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">false</_x5b9f__x88c5_>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27817FF2-F49B-48C7-B495-DA609CB0DD24}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B48DB0D-B5D1-462E-89C6-32857537C424}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="0c73c1f5-50cd-4477-a315-44bef7b8a847"/>
-    <ds:schemaRef ds:uri="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -58195,9 +58094,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B48DB0D-B5D1-462E-89C6-32857537C424}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27817FF2-F49B-48C7-B495-DA609CB0DD24}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="0c73c1f5-50cd-4477-a315-44bef7b8a847"/>
+    <ds:schemaRef ds:uri="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/01_企画/【ガント】PAW！.xlsx
+++ b/01_企画/【ガント】PAW！.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2416009\Project\PAW\01_企画\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B56891D8-CF55-45CC-AB6B-436E17CCFC46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30673017-39E5-47D0-A2A1-94648899F56A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14325" yWindow="5580" windowWidth="11115" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="スケジュール" sheetId="7" r:id="rId1"/>
@@ -12870,7 +12870,9 @@
       <c r="F20" s="17">
         <v>46293</v>
       </c>
-      <c r="G20" s="17"/>
+      <c r="G20" s="17">
+        <v>46295</v>
+      </c>
       <c r="H20" s="18" t="str">
         <f t="shared" ca="1" si="22"/>
         <v/>
@@ -12937,7 +12939,7 @@
       </c>
       <c r="X20" s="18" t="str">
         <f t="shared" ca="1" si="23"/>
-        <v/>
+        <v>→</v>
       </c>
       <c r="Y20" s="18" t="str">
         <f t="shared" ca="1" si="23"/>
@@ -13421,7 +13423,9 @@
       <c r="F21" s="17">
         <v>46294</v>
       </c>
-      <c r="G21" s="17"/>
+      <c r="G21" s="17">
+        <v>46295</v>
+      </c>
       <c r="H21" s="18" t="str">
         <f t="shared" ca="1" si="22"/>
         <v/>
@@ -13488,7 +13492,7 @@
       </c>
       <c r="X21" s="18" t="str">
         <f t="shared" ca="1" si="23"/>
-        <v/>
+        <v>→</v>
       </c>
       <c r="Y21" s="18" t="str">
         <f t="shared" ca="1" si="23"/>
@@ -57779,12 +57783,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_x5b9f__x88c5_ xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">false</_x5b9f__x88c5_>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -58055,21 +58062,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_x5b9f__x88c5_ xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">false</_x5b9f__x88c5_>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B48DB0D-B5D1-462E-89C6-32857537C424}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27817FF2-F49B-48C7-B495-DA609CB0DD24}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="0c73c1f5-50cd-4477-a315-44bef7b8a847"/>
+    <ds:schemaRef ds:uri="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -58094,12 +58101,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27817FF2-F49B-48C7-B495-DA609CB0DD24}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B48DB0D-B5D1-462E-89C6-32857537C424}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="0c73c1f5-50cd-4477-a315-44bef7b8a847"/>
-    <ds:schemaRef ds:uri="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/01_企画/【ガント】PAW！.xlsx
+++ b/01_企画/【ガント】PAW！.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2416009\Project\PAW\01_企画\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\suire\OneDrive\デスクトップ\【就職作品】PAW！\00_Git\01_企画\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30673017-39E5-47D0-A2A1-94648899F56A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1806B4F7-40A1-4288-875F-99C8E36F5D3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14325" yWindow="5580" windowWidth="11115" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="スケジュール" sheetId="7" r:id="rId1"/>
@@ -39,9 +39,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -1638,487 +1635,11 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="100">
+  <dxfs count="82">
     <dxf>
       <fill>
         <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="22"/>
+          <bgColor indexed="50"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2139,7 +1660,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor indexed="50"/>
+          <bgColor indexed="42"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2147,13 +1668,6 @@
       <fill>
         <patternFill>
           <bgColor indexed="47"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="42"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2188,48 +1702,6 @@
       <fill>
         <patternFill>
           <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="41"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2285,6 +1757,195 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor indexed="41"/>
         </patternFill>
       </fill>
@@ -2300,6 +1961,216 @@
       <fill>
         <patternFill>
           <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor indexed="41"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -11766,7 +11637,9 @@
       <c r="F18" s="17">
         <v>46289</v>
       </c>
-      <c r="G18" s="17"/>
+      <c r="G18" s="17">
+        <v>46298</v>
+      </c>
       <c r="H18" s="18" t="str">
         <f t="shared" ca="1" si="22"/>
         <v/>
@@ -11845,7 +11718,7 @@
       </c>
       <c r="AA18" s="18" t="str">
         <f t="shared" ca="1" si="23"/>
-        <v/>
+        <v>→</v>
       </c>
       <c r="AB18" s="18" t="str">
         <f t="shared" ca="1" si="24"/>
@@ -13976,7 +13849,9 @@
       <c r="F22" s="17">
         <v>46296</v>
       </c>
-      <c r="G22" s="17"/>
+      <c r="G22" s="17">
+        <v>46299</v>
+      </c>
       <c r="H22" s="18" t="str">
         <f t="shared" ca="1" si="22"/>
         <v/>
@@ -14059,7 +13934,7 @@
       </c>
       <c r="AB22" s="18" t="str">
         <f t="shared" ca="1" si="24"/>
-        <v/>
+        <v>→</v>
       </c>
       <c r="AC22" s="18" t="str">
         <f t="shared" ca="1" si="24"/>
@@ -57395,373 +57270,291 @@
   </mergeCells>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="A36:A39">
-    <cfRule type="expression" dxfId="99" priority="736" stopIfTrue="1">
+    <cfRule type="expression" dxfId="81" priority="736" stopIfTrue="1">
       <formula>OR(AND(ISBLANK($E35)=TRUE,ISBLANK($D35)=FALSE,$D35&lt;=TODAY()),AND(ISBLANK($G35)=TRUE,ISBLANK($F35)=FALSE,$F35&lt;TODAY()))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="98" priority="735" stopIfTrue="1">
+    <cfRule type="expression" dxfId="80" priority="735" stopIfTrue="1">
       <formula>ISBLANK($G35)=FALSE</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="97" priority="737" stopIfTrue="1">
+    <cfRule type="expression" dxfId="79" priority="737" stopIfTrue="1">
       <formula>AND(ISBLANK($D35)=FALSE,ISBLANK($E35)=FALSE,$E35&lt;=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A7:G7 A8 A9:G15 A16 A44:G101 D25:F27 A24:A28 C30:G30 A43:F43 C42:F43 A27:G29 G38:G43 G31:G35 A35:F35 A30:A36 A36:G37 A17:G23 D24:G26 D31:F32 C32:F35 A37:F39 A40 A42:A43 D40:F41 A41:F41">
-    <cfRule type="expression" dxfId="96" priority="192" stopIfTrue="1">
+  <conditionalFormatting sqref="A41">
+    <cfRule type="expression" dxfId="78" priority="27" stopIfTrue="1">
+      <formula>AND(ISBLANK($D40)=FALSE,ISBLANK($E40)=FALSE,$E40&lt;=TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="77" priority="26" stopIfTrue="1">
+      <formula>OR(AND(ISBLANK($E40)=TRUE,ISBLANK($D40)=FALSE,$D40&lt;=TODAY()),AND(ISBLANK($G40)=TRUE,ISBLANK($F40)=FALSE,$F40&lt;TODAY()))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="76" priority="25" stopIfTrue="1">
+      <formula>ISBLANK($G40)=FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A7:G7 A8 A9:G15 A16 A17:G23 D24:G26 A24:A28 D25:F27 A27:G29 C30:G30 A30:A36 D31:F32 G31:G35 C32:F35 A35:F35 A36:G37 A37:F39 G38:G43 A40 D40:F41 A41:F41 A42:A43 C42:F43 A43:F43 A44:G101">
+    <cfRule type="expression" dxfId="75" priority="191" stopIfTrue="1">
+      <formula>OR(AND(ISBLANK($E7)=TRUE,ISBLANK($D7)=FALSE,$D7&lt;=TODAY()),AND(ISBLANK($G7)=TRUE,ISBLANK($F7)=FALSE,$F7&lt;TODAY()))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="74" priority="192" stopIfTrue="1">
       <formula>AND(ISBLANK($D7)=FALSE,ISBLANK($E7)=FALSE,$E7&lt;=TODAY())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="95" priority="191" stopIfTrue="1">
-      <formula>OR(AND(ISBLANK($E7)=TRUE,ISBLANK($D7)=FALSE,$D7&lt;=TODAY()),AND(ISBLANK($G7)=TRUE,ISBLANK($F7)=FALSE,$F7&lt;TODAY()))</formula>
-    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A7:G7 A8 A9:G15 A16 A44:G101 D25:F27 A24:A28 C30:G30 A43:F43 C42:F43 A27:G29 G38:G43 G31:G35 A35:F35 A30:A36 A36:G37 A17:G23 D24:G26 D31:F32 C32:F35 A37:F39 A40 A42:A43 D40:F41 A41:F41">
-    <cfRule type="expression" dxfId="94" priority="190" stopIfTrue="1">
+  <conditionalFormatting sqref="A36:G37 A37:F39 A27:G29 C30:G30 A43:F43 A35:F35 C32:F35 A41:F41 A7:G7 A8 A9:G15 A16 A17:G23 D24:G26 A24:A28 D25:F27 A30:A36 D31:F32 G31:G35 G38:G43 A40 D40:F41 A42:A43 C42:F43 A44:G101">
+    <cfRule type="expression" dxfId="73" priority="190" stopIfTrue="1">
       <formula>ISBLANK($G7)=FALSE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B28 B30">
-    <cfRule type="expression" dxfId="93" priority="91" stopIfTrue="1">
-      <formula>ISBLANK($G24)=FALSE</formula>
+  <conditionalFormatting sqref="B31:B36">
+    <cfRule type="expression" dxfId="72" priority="58" stopIfTrue="1">
+      <formula>ISBLANK($G27)=FALSE</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="92" priority="92" stopIfTrue="1">
-      <formula>OR(AND(ISBLANK($E24)=TRUE,ISBLANK($D24)=FALSE,$D24&lt;=TODAY()),AND(ISBLANK($G24)=TRUE,ISBLANK($F24)=FALSE,$F24&lt;TODAY()))</formula>
+    <cfRule type="expression" dxfId="71" priority="60" stopIfTrue="1">
+      <formula>AND(ISBLANK($D27)=FALSE,ISBLANK($E27)=FALSE,$E27&lt;=TODAY())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="91" priority="93" stopIfTrue="1">
-      <formula>AND(ISBLANK($D24)=FALSE,ISBLANK($E24)=FALSE,$E24&lt;=TODAY())</formula>
+    <cfRule type="expression" dxfId="70" priority="59" stopIfTrue="1">
+      <formula>OR(AND(ISBLANK($E27)=TRUE,ISBLANK($D27)=FALSE,$D27&lt;=TODAY()),AND(ISBLANK($G27)=TRUE,ISBLANK($F27)=FALSE,$F27&lt;TODAY()))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36:B39">
-    <cfRule type="expression" dxfId="90" priority="76" stopIfTrue="1">
+    <cfRule type="expression" dxfId="69" priority="78" stopIfTrue="1">
+      <formula>AND(ISBLANK($D36)=FALSE,ISBLANK($E36)=FALSE,$E36&lt;=TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="68" priority="77" stopIfTrue="1">
+      <formula>OR(AND(ISBLANK($E36)=TRUE,ISBLANK($D36)=FALSE,$D36&lt;=TODAY()),AND(ISBLANK($G36)=TRUE,ISBLANK($F36)=FALSE,$F36&lt;TODAY()))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="67" priority="76" stopIfTrue="1">
       <formula>ISBLANK($G36)=FALSE</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="89" priority="77" stopIfTrue="1">
-      <formula>OR(AND(ISBLANK($E36)=TRUE,ISBLANK($D36)=FALSE,$D36&lt;=TODAY()),AND(ISBLANK($G36)=TRUE,ISBLANK($F36)=FALSE,$F36&lt;TODAY()))</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B41">
+    <cfRule type="expression" dxfId="66" priority="20" stopIfTrue="1">
+      <formula>OR(AND(ISBLANK($E41)=TRUE,ISBLANK($D41)=FALSE,$D41&lt;=TODAY()),AND(ISBLANK($G41)=TRUE,ISBLANK($F41)=FALSE,$F41&lt;TODAY()))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="88" priority="78" stopIfTrue="1">
-      <formula>AND(ISBLANK($D36)=FALSE,ISBLANK($E36)=FALSE,$E36&lt;=TODAY())</formula>
+    <cfRule type="expression" dxfId="65" priority="21" stopIfTrue="1">
+      <formula>AND(ISBLANK($D41)=FALSE,ISBLANK($E41)=FALSE,$E41&lt;=TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="64" priority="19" stopIfTrue="1">
+      <formula>ISBLANK($G41)=FALSE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B24:C27">
-    <cfRule type="expression" dxfId="87" priority="102" stopIfTrue="1">
+  <conditionalFormatting sqref="B42:B43">
+    <cfRule type="expression" dxfId="63" priority="72" stopIfTrue="1">
+      <formula>AND(ISBLANK($D38)=FALSE,ISBLANK($E38)=FALSE,$E38&lt;=TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="62" priority="71" stopIfTrue="1">
+      <formula>OR(AND(ISBLANK($E38)=TRUE,ISBLANK($D38)=FALSE,$D38&lt;=TODAY()),AND(ISBLANK($G38)=TRUE,ISBLANK($F38)=FALSE,$F38&lt;TODAY()))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="61" priority="70" stopIfTrue="1">
+      <formula>ISBLANK($G38)=FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B24:C28 B30:C30">
+    <cfRule type="expression" dxfId="60" priority="88" stopIfTrue="1">
+      <formula>ISBLANK($G20)=FALSE</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="59" priority="90" stopIfTrue="1">
       <formula>AND(ISBLANK($D20)=FALSE,ISBLANK($E20)=FALSE,$E20&lt;=TODAY())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="86" priority="100" stopIfTrue="1">
-      <formula>ISBLANK($G20)=FALSE</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="85" priority="101" stopIfTrue="1">
+    <cfRule type="expression" dxfId="58" priority="89" stopIfTrue="1">
       <formula>OR(AND(ISBLANK($E20)=TRUE,ISBLANK($D20)=FALSE,$D20&lt;=TODAY()),AND(ISBLANK($G20)=TRUE,ISBLANK($F20)=FALSE,$F20&lt;TODAY()))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B36:C36">
-    <cfRule type="expression" dxfId="84" priority="117" stopIfTrue="1">
+    <cfRule type="expression" dxfId="57" priority="115" stopIfTrue="1">
+      <formula>ISBLANK($G24)=FALSE</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="56" priority="116" stopIfTrue="1">
+      <formula>OR(AND(ISBLANK($E24)=TRUE,ISBLANK($D24)=FALSE,$D24&lt;=TODAY()),AND(ISBLANK($G24)=TRUE,ISBLANK($F24)=FALSE,$F24&lt;TODAY()))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="55" priority="117" stopIfTrue="1">
       <formula>AND(ISBLANK($D24)=FALSE,ISBLANK($E24)=FALSE,$E24&lt;=TODAY())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="83" priority="116" stopIfTrue="1">
-      <formula>OR(AND(ISBLANK($E24)=TRUE,ISBLANK($D24)=FALSE,$D24&lt;=TODAY()),AND(ISBLANK($G24)=TRUE,ISBLANK($F24)=FALSE,$F24&lt;TODAY()))</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B37:C38">
+    <cfRule type="expression" dxfId="54" priority="63" stopIfTrue="1">
+      <formula>AND(ISBLANK($D25)=FALSE,ISBLANK($E25)=FALSE,$E25&lt;=TODAY())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="82" priority="115" stopIfTrue="1">
-      <formula>ISBLANK($G24)=FALSE</formula>
+    <cfRule type="expression" dxfId="53" priority="62" stopIfTrue="1">
+      <formula>OR(AND(ISBLANK($E25)=TRUE,ISBLANK($D25)=FALSE,$D25&lt;=TODAY()),AND(ISBLANK($G25)=TRUE,ISBLANK($F25)=FALSE,$F25&lt;TODAY()))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="52" priority="51" stopIfTrue="1">
+      <formula>AND(ISBLANK($D25)=FALSE,ISBLANK($E25)=FALSE,$E25&lt;=TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="51" priority="50" stopIfTrue="1">
+      <formula>OR(AND(ISBLANK($E25)=TRUE,ISBLANK($D25)=FALSE,$D25&lt;=TODAY()),AND(ISBLANK($G25)=TRUE,ISBLANK($F25)=FALSE,$F25&lt;TODAY()))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="50" priority="61" stopIfTrue="1">
+      <formula>ISBLANK($G25)=FALSE</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="49" priority="49" stopIfTrue="1">
+      <formula>ISBLANK($G25)=FALSE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C28 C30">
-    <cfRule type="expression" dxfId="81" priority="90" stopIfTrue="1">
-      <formula>AND(ISBLANK($D24)=FALSE,ISBLANK($E24)=FALSE,$E24&lt;=TODAY())</formula>
+  <conditionalFormatting sqref="B38:C38">
+    <cfRule type="expression" dxfId="48" priority="31" stopIfTrue="1">
+      <formula>ISBLANK($G26)=FALSE</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="80" priority="89" stopIfTrue="1">
-      <formula>OR(AND(ISBLANK($E24)=TRUE,ISBLANK($D24)=FALSE,$D24&lt;=TODAY()),AND(ISBLANK($G24)=TRUE,ISBLANK($F24)=FALSE,$F24&lt;TODAY()))</formula>
+    <cfRule type="expression" dxfId="47" priority="33" stopIfTrue="1">
+      <formula>AND(ISBLANK($D26)=FALSE,ISBLANK($E26)=FALSE,$E26&lt;=TODAY())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="79" priority="88" stopIfTrue="1">
-      <formula>ISBLANK($G24)=FALSE</formula>
+    <cfRule type="expression" dxfId="46" priority="32" stopIfTrue="1">
+      <formula>OR(AND(ISBLANK($E26)=TRUE,ISBLANK($D26)=FALSE,$D26&lt;=TODAY()),AND(ISBLANK($G26)=TRUE,ISBLANK($F26)=FALSE,$F26&lt;TODAY()))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="45" priority="28" stopIfTrue="1">
+      <formula>ISBLANK($G26)=FALSE</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="44" priority="29" stopIfTrue="1">
+      <formula>OR(AND(ISBLANK($E26)=TRUE,ISBLANK($D26)=FALSE,$D26&lt;=TODAY()),AND(ISBLANK($G26)=TRUE,ISBLANK($F26)=FALSE,$F26&lt;TODAY()))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="43" priority="30" stopIfTrue="1">
+      <formula>AND(ISBLANK($D26)=FALSE,ISBLANK($E26)=FALSE,$E26&lt;=TODAY())</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B38:C39">
+    <cfRule type="expression" dxfId="42" priority="34" stopIfTrue="1">
+      <formula>ISBLANK($G26)=FALSE</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="41" priority="44" stopIfTrue="1">
+      <formula>OR(AND(ISBLANK($E26)=TRUE,ISBLANK($D26)=FALSE,$D26&lt;=TODAY()),AND(ISBLANK($G26)=TRUE,ISBLANK($F26)=FALSE,$F26&lt;TODAY()))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="40" priority="43" stopIfTrue="1">
+      <formula>ISBLANK($G26)=FALSE</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="39" priority="36" stopIfTrue="1">
+      <formula>AND(ISBLANK($D26)=FALSE,ISBLANK($E26)=FALSE,$E26&lt;=TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="38" priority="45" stopIfTrue="1">
+      <formula>AND(ISBLANK($D26)=FALSE,ISBLANK($E26)=FALSE,$E26&lt;=TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="37" priority="35" stopIfTrue="1">
+      <formula>OR(AND(ISBLANK($E26)=TRUE,ISBLANK($D26)=FALSE,$D26&lt;=TODAY()),AND(ISBLANK($G26)=TRUE,ISBLANK($F26)=FALSE,$F26&lt;TODAY()))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B39:C39">
+    <cfRule type="expression" dxfId="36" priority="42" stopIfTrue="1">
+      <formula>AND(ISBLANK($D27)=FALSE,ISBLANK($E27)=FALSE,$E27&lt;=TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="35" priority="41" stopIfTrue="1">
+      <formula>OR(AND(ISBLANK($E27)=TRUE,ISBLANK($D27)=FALSE,$D27&lt;=TODAY()),AND(ISBLANK($G27)=TRUE,ISBLANK($F27)=FALSE,$F27&lt;TODAY()))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="34" priority="40" stopIfTrue="1">
+      <formula>ISBLANK($G27)=FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B41:C41">
+    <cfRule type="expression" dxfId="33" priority="3" stopIfTrue="1">
+      <formula>AND(ISBLANK($D29)=FALSE,ISBLANK($E29)=FALSE,$E29&lt;=TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="32" priority="4" stopIfTrue="1">
+      <formula>ISBLANK($G29)=FALSE</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="31" priority="9" stopIfTrue="1">
+      <formula>AND(ISBLANK($D29)=FALSE,ISBLANK($E29)=FALSE,$E29&lt;=TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="8" stopIfTrue="1">
+      <formula>OR(AND(ISBLANK($E29)=TRUE,ISBLANK($D29)=FALSE,$D29&lt;=TODAY()),AND(ISBLANK($G29)=TRUE,ISBLANK($F29)=FALSE,$F29&lt;TODAY()))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="29" priority="1" stopIfTrue="1">
+      <formula>ISBLANK($G29)=FALSE</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="28" priority="2" stopIfTrue="1">
+      <formula>OR(AND(ISBLANK($E29)=TRUE,ISBLANK($D29)=FALSE,$D29&lt;=TODAY()),AND(ISBLANK($G29)=TRUE,ISBLANK($F29)=FALSE,$F29&lt;TODAY()))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="27" priority="7" stopIfTrue="1">
+      <formula>ISBLANK($G29)=FALSE</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="16" stopIfTrue="1">
+      <formula>ISBLANK($G29)=FALSE</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="25" priority="6" stopIfTrue="1">
+      <formula>AND(ISBLANK($D29)=FALSE,ISBLANK($E29)=FALSE,$E29&lt;=TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="11" stopIfTrue="1">
+      <formula>OR(AND(ISBLANK($E29)=TRUE,ISBLANK($D29)=FALSE,$D29&lt;=TODAY()),AND(ISBLANK($G29)=TRUE,ISBLANK($F29)=FALSE,$F29&lt;TODAY()))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="23" priority="18" stopIfTrue="1">
+      <formula>AND(ISBLANK($D29)=FALSE,ISBLANK($E29)=FALSE,$E29&lt;=TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="17" stopIfTrue="1">
+      <formula>OR(AND(ISBLANK($E29)=TRUE,ISBLANK($D29)=FALSE,$D29&lt;=TODAY()),AND(ISBLANK($G29)=TRUE,ISBLANK($F29)=FALSE,$F29&lt;TODAY()))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="5" stopIfTrue="1">
+      <formula>OR(AND(ISBLANK($E29)=TRUE,ISBLANK($D29)=FALSE,$D29&lt;=TODAY()),AND(ISBLANK($G29)=TRUE,ISBLANK($F29)=FALSE,$F29&lt;TODAY()))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="20" priority="15" stopIfTrue="1">
+      <formula>AND(ISBLANK($D29)=FALSE,ISBLANK($E29)=FALSE,$E29&lt;=TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="14" stopIfTrue="1">
+      <formula>OR(AND(ISBLANK($E29)=TRUE,ISBLANK($D29)=FALSE,$D29&lt;=TODAY()),AND(ISBLANK($G29)=TRUE,ISBLANK($F29)=FALSE,$F29&lt;TODAY()))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="13" stopIfTrue="1">
+      <formula>ISBLANK($G29)=FALSE</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="12" stopIfTrue="1">
+      <formula>AND(ISBLANK($D29)=FALSE,ISBLANK($E29)=FALSE,$E29&lt;=TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="16" priority="10" stopIfTrue="1">
+      <formula>ISBLANK($G29)=FALSE</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C31:C32">
+    <cfRule type="expression" dxfId="15" priority="55" stopIfTrue="1">
+      <formula>ISBLANK($G27)=FALSE</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="56" stopIfTrue="1">
+      <formula>OR(AND(ISBLANK($E27)=TRUE,ISBLANK($D27)=FALSE,$D27&lt;=TODAY()),AND(ISBLANK($G27)=TRUE,ISBLANK($F27)=FALSE,$F27&lt;TODAY()))</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="57" stopIfTrue="1">
+      <formula>AND(ISBLANK($D27)=FALSE,ISBLANK($E27)=FALSE,$E27&lt;=TODAY())</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C36:C39">
-    <cfRule type="expression" dxfId="78" priority="96" stopIfTrue="1">
+    <cfRule type="expression" dxfId="12" priority="96" stopIfTrue="1">
       <formula>AND(ISBLANK($D32)=FALSE,ISBLANK($E32)=FALSE,$E32&lt;=TODAY())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="77" priority="94" stopIfTrue="1">
+    <cfRule type="expression" dxfId="11" priority="94" stopIfTrue="1">
       <formula>ISBLANK($G32)=FALSE</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="76" priority="95" stopIfTrue="1">
+    <cfRule type="expression" dxfId="10" priority="95" stopIfTrue="1">
       <formula>OR(AND(ISBLANK($E32)=TRUE,ISBLANK($D32)=FALSE,$D32&lt;=TODAY()),AND(ISBLANK($G32)=TRUE,ISBLANK($F32)=FALSE,$F32&lt;TODAY()))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C41">
+    <cfRule type="expression" dxfId="9" priority="24" stopIfTrue="1">
+      <formula>AND(ISBLANK($D37)=FALSE,ISBLANK($E37)=FALSE,$E37&lt;=TODAY())</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="22" stopIfTrue="1">
+      <formula>ISBLANK($G37)=FALSE</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="23" stopIfTrue="1">
+      <formula>OR(AND(ISBLANK($E37)=TRUE,ISBLANK($D37)=FALSE,$D37&lt;=TODAY()),AND(ISBLANK($G37)=TRUE,ISBLANK($F37)=FALSE,$F37&lt;TODAY()))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="H3:IQ3">
-    <cfRule type="expression" dxfId="75" priority="719" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="719" stopIfTrue="1">
       <formula>AND(DAY(H4)&gt;=1,DAY(H4)&lt;=$K$2)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:IQ5">
-    <cfRule type="expression" dxfId="74" priority="720" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="720" stopIfTrue="1">
       <formula>AND(H$4&lt;=TODAY(),H$4+$K$2-1&gt;=TODAY())</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="73" priority="722" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="721" stopIfTrue="1">
+      <formula>WEEKDAY(H$4)=1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="722" stopIfTrue="1">
       <formula>WEEKDAY(H$4)=7</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="72" priority="721" stopIfTrue="1">
-      <formula>WEEKDAY(H$4)=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H7:IQ101">
-    <cfRule type="expression" dxfId="71" priority="723" stopIfTrue="1">
-      <formula>OR(AND($D7&gt;=H$4,$D7&lt;=H$4+$K$2-1),AND($F7&gt;=H$4,$F7&lt;=H$4+$K$2-1),AND($D7&lt;H$4,$F7&gt;H$4+$K$2-1))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="70" priority="724" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="724" stopIfTrue="1">
       <formula>WEEKDAY(H$4)=1</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="69" priority="725" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="725" stopIfTrue="1">
       <formula>WEEKDAY(H$4)=7</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B42:B43">
-    <cfRule type="expression" dxfId="68" priority="70" stopIfTrue="1">
-      <formula>ISBLANK($G38)=FALSE</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="67" priority="71" stopIfTrue="1">
-      <formula>OR(AND(ISBLANK($E38)=TRUE,ISBLANK($D38)=FALSE,$D38&lt;=TODAY()),AND(ISBLANK($G38)=TRUE,ISBLANK($F38)=FALSE,$F38&lt;TODAY()))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="66" priority="72" stopIfTrue="1">
-      <formula>AND(ISBLANK($D38)=FALSE,ISBLANK($E38)=FALSE,$E38&lt;=TODAY())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B37:C37">
-    <cfRule type="expression" dxfId="65" priority="64" stopIfTrue="1">
-      <formula>ISBLANK($G25)=FALSE</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="64" priority="65" stopIfTrue="1">
-      <formula>OR(AND(ISBLANK($E25)=TRUE,ISBLANK($D25)=FALSE,$D25&lt;=TODAY()),AND(ISBLANK($G25)=TRUE,ISBLANK($F25)=FALSE,$F25&lt;TODAY()))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="63" priority="66" stopIfTrue="1">
-      <formula>AND(ISBLANK($D25)=FALSE,ISBLANK($E25)=FALSE,$E25&lt;=TODAY())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B38:C38">
-    <cfRule type="expression" dxfId="62" priority="61" stopIfTrue="1">
-      <formula>ISBLANK($G26)=FALSE</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="61" priority="62" stopIfTrue="1">
-      <formula>OR(AND(ISBLANK($E26)=TRUE,ISBLANK($D26)=FALSE,$D26&lt;=TODAY()),AND(ISBLANK($G26)=TRUE,ISBLANK($F26)=FALSE,$F26&lt;TODAY()))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="60" priority="63" stopIfTrue="1">
-      <formula>AND(ISBLANK($D26)=FALSE,ISBLANK($E26)=FALSE,$E26&lt;=TODAY())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B31:B36">
-    <cfRule type="expression" dxfId="59" priority="58" stopIfTrue="1">
-      <formula>ISBLANK($G27)=FALSE</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="58" priority="59" stopIfTrue="1">
-      <formula>OR(AND(ISBLANK($E27)=TRUE,ISBLANK($D27)=FALSE,$D27&lt;=TODAY()),AND(ISBLANK($G27)=TRUE,ISBLANK($F27)=FALSE,$F27&lt;TODAY()))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="57" priority="60" stopIfTrue="1">
-      <formula>AND(ISBLANK($D27)=FALSE,ISBLANK($E27)=FALSE,$E27&lt;=TODAY())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C31:C32">
-    <cfRule type="expression" dxfId="56" priority="55" stopIfTrue="1">
-      <formula>ISBLANK($G27)=FALSE</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="55" priority="56" stopIfTrue="1">
-      <formula>OR(AND(ISBLANK($E27)=TRUE,ISBLANK($D27)=FALSE,$D27&lt;=TODAY()),AND(ISBLANK($G27)=TRUE,ISBLANK($F27)=FALSE,$F27&lt;TODAY()))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="54" priority="57" stopIfTrue="1">
-      <formula>AND(ISBLANK($D27)=FALSE,ISBLANK($E27)=FALSE,$E27&lt;=TODAY())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B37:C37">
-    <cfRule type="expression" dxfId="53" priority="52" stopIfTrue="1">
-      <formula>ISBLANK($G25)=FALSE</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="52" priority="53" stopIfTrue="1">
-      <formula>OR(AND(ISBLANK($E25)=TRUE,ISBLANK($D25)=FALSE,$D25&lt;=TODAY()),AND(ISBLANK($G25)=TRUE,ISBLANK($F25)=FALSE,$F25&lt;TODAY()))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="51" priority="54" stopIfTrue="1">
-      <formula>AND(ISBLANK($D25)=FALSE,ISBLANK($E25)=FALSE,$E25&lt;=TODAY())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B38:C38">
-    <cfRule type="expression" dxfId="50" priority="49" stopIfTrue="1">
-      <formula>ISBLANK($G26)=FALSE</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="49" priority="50" stopIfTrue="1">
-      <formula>OR(AND(ISBLANK($E26)=TRUE,ISBLANK($D26)=FALSE,$D26&lt;=TODAY()),AND(ISBLANK($G26)=TRUE,ISBLANK($F26)=FALSE,$F26&lt;TODAY()))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="48" priority="51" stopIfTrue="1">
-      <formula>AND(ISBLANK($D26)=FALSE,ISBLANK($E26)=FALSE,$E26&lt;=TODAY())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B38:C38">
-    <cfRule type="expression" dxfId="47" priority="46" stopIfTrue="1">
-      <formula>ISBLANK($G26)=FALSE</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="46" priority="47" stopIfTrue="1">
-      <formula>OR(AND(ISBLANK($E26)=TRUE,ISBLANK($D26)=FALSE,$D26&lt;=TODAY()),AND(ISBLANK($G26)=TRUE,ISBLANK($F26)=FALSE,$F26&lt;TODAY()))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="45" priority="48" stopIfTrue="1">
-      <formula>AND(ISBLANK($D26)=FALSE,ISBLANK($E26)=FALSE,$E26&lt;=TODAY())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B39:C39">
-    <cfRule type="expression" dxfId="44" priority="43" stopIfTrue="1">
-      <formula>ISBLANK($G27)=FALSE</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="43" priority="44" stopIfTrue="1">
-      <formula>OR(AND(ISBLANK($E27)=TRUE,ISBLANK($D27)=FALSE,$D27&lt;=TODAY()),AND(ISBLANK($G27)=TRUE,ISBLANK($F27)=FALSE,$F27&lt;TODAY()))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="42" priority="45" stopIfTrue="1">
-      <formula>AND(ISBLANK($D27)=FALSE,ISBLANK($E27)=FALSE,$E27&lt;=TODAY())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B39:C39">
-    <cfRule type="expression" dxfId="41" priority="40" stopIfTrue="1">
-      <formula>ISBLANK($G27)=FALSE</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="40" priority="41" stopIfTrue="1">
-      <formula>OR(AND(ISBLANK($E27)=TRUE,ISBLANK($D27)=FALSE,$D27&lt;=TODAY()),AND(ISBLANK($G27)=TRUE,ISBLANK($F27)=FALSE,$F27&lt;TODAY()))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="39" priority="42" stopIfTrue="1">
-      <formula>AND(ISBLANK($D27)=FALSE,ISBLANK($E27)=FALSE,$E27&lt;=TODAY())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B39:C39">
-    <cfRule type="expression" dxfId="38" priority="37" stopIfTrue="1">
-      <formula>ISBLANK($G27)=FALSE</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="37" priority="38" stopIfTrue="1">
-      <formula>OR(AND(ISBLANK($E27)=TRUE,ISBLANK($D27)=FALSE,$D27&lt;=TODAY()),AND(ISBLANK($G27)=TRUE,ISBLANK($F27)=FALSE,$F27&lt;TODAY()))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="36" priority="39" stopIfTrue="1">
-      <formula>AND(ISBLANK($D27)=FALSE,ISBLANK($E27)=FALSE,$E27&lt;=TODAY())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B38:C38">
-    <cfRule type="expression" dxfId="35" priority="34" stopIfTrue="1">
-      <formula>ISBLANK($G26)=FALSE</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="34" priority="35" stopIfTrue="1">
-      <formula>OR(AND(ISBLANK($E26)=TRUE,ISBLANK($D26)=FALSE,$D26&lt;=TODAY()),AND(ISBLANK($G26)=TRUE,ISBLANK($F26)=FALSE,$F26&lt;TODAY()))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="33" priority="36" stopIfTrue="1">
-      <formula>AND(ISBLANK($D26)=FALSE,ISBLANK($E26)=FALSE,$E26&lt;=TODAY())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B38:C38">
-    <cfRule type="expression" dxfId="32" priority="31" stopIfTrue="1">
-      <formula>ISBLANK($G26)=FALSE</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="31" priority="32" stopIfTrue="1">
-      <formula>OR(AND(ISBLANK($E26)=TRUE,ISBLANK($D26)=FALSE,$D26&lt;=TODAY()),AND(ISBLANK($G26)=TRUE,ISBLANK($F26)=FALSE,$F26&lt;TODAY()))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="30" priority="33" stopIfTrue="1">
-      <formula>AND(ISBLANK($D26)=FALSE,ISBLANK($E26)=FALSE,$E26&lt;=TODAY())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B38:C38">
-    <cfRule type="expression" dxfId="29" priority="28" stopIfTrue="1">
-      <formula>ISBLANK($G26)=FALSE</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="29" stopIfTrue="1">
-      <formula>OR(AND(ISBLANK($E26)=TRUE,ISBLANK($D26)=FALSE,$D26&lt;=TODAY()),AND(ISBLANK($G26)=TRUE,ISBLANK($F26)=FALSE,$F26&lt;TODAY()))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="27" priority="30" stopIfTrue="1">
-      <formula>AND(ISBLANK($D26)=FALSE,ISBLANK($E26)=FALSE,$E26&lt;=TODAY())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A41">
-    <cfRule type="expression" dxfId="26" priority="25" stopIfTrue="1">
-      <formula>ISBLANK($G40)=FALSE</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="25" priority="26" stopIfTrue="1">
-      <formula>OR(AND(ISBLANK($E40)=TRUE,ISBLANK($D40)=FALSE,$D40&lt;=TODAY()),AND(ISBLANK($G40)=TRUE,ISBLANK($F40)=FALSE,$F40&lt;TODAY()))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="24" priority="27" stopIfTrue="1">
-      <formula>AND(ISBLANK($D40)=FALSE,ISBLANK($E40)=FALSE,$E40&lt;=TODAY())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B41">
-    <cfRule type="expression" dxfId="23" priority="19" stopIfTrue="1">
-      <formula>ISBLANK($G41)=FALSE</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="22" priority="20" stopIfTrue="1">
-      <formula>OR(AND(ISBLANK($E41)=TRUE,ISBLANK($D41)=FALSE,$D41&lt;=TODAY()),AND(ISBLANK($G41)=TRUE,ISBLANK($F41)=FALSE,$F41&lt;TODAY()))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="21" priority="21" stopIfTrue="1">
-      <formula>AND(ISBLANK($D41)=FALSE,ISBLANK($E41)=FALSE,$E41&lt;=TODAY())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C41">
-    <cfRule type="expression" dxfId="20" priority="22" stopIfTrue="1">
-      <formula>ISBLANK($G37)=FALSE</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="19" priority="23" stopIfTrue="1">
-      <formula>OR(AND(ISBLANK($E37)=TRUE,ISBLANK($D37)=FALSE,$D37&lt;=TODAY()),AND(ISBLANK($G37)=TRUE,ISBLANK($F37)=FALSE,$F37&lt;TODAY()))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="18" priority="24" stopIfTrue="1">
-      <formula>AND(ISBLANK($D37)=FALSE,ISBLANK($E37)=FALSE,$E37&lt;=TODAY())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B41:C41">
-    <cfRule type="expression" dxfId="17" priority="16" stopIfTrue="1">
-      <formula>ISBLANK($G29)=FALSE</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="16" priority="17" stopIfTrue="1">
-      <formula>OR(AND(ISBLANK($E29)=TRUE,ISBLANK($D29)=FALSE,$D29&lt;=TODAY()),AND(ISBLANK($G29)=TRUE,ISBLANK($F29)=FALSE,$F29&lt;TODAY()))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="15" priority="18" stopIfTrue="1">
-      <formula>AND(ISBLANK($D29)=FALSE,ISBLANK($E29)=FALSE,$E29&lt;=TODAY())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B41:C41">
-    <cfRule type="expression" dxfId="14" priority="13" stopIfTrue="1">
-      <formula>ISBLANK($G29)=FALSE</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="13" priority="14" stopIfTrue="1">
-      <formula>OR(AND(ISBLANK($E29)=TRUE,ISBLANK($D29)=FALSE,$D29&lt;=TODAY()),AND(ISBLANK($G29)=TRUE,ISBLANK($F29)=FALSE,$F29&lt;TODAY()))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="12" priority="15" stopIfTrue="1">
-      <formula>AND(ISBLANK($D29)=FALSE,ISBLANK($E29)=FALSE,$E29&lt;=TODAY())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B41:C41">
-    <cfRule type="expression" dxfId="11" priority="10" stopIfTrue="1">
-      <formula>ISBLANK($G29)=FALSE</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="10" priority="11" stopIfTrue="1">
-      <formula>OR(AND(ISBLANK($E29)=TRUE,ISBLANK($D29)=FALSE,$D29&lt;=TODAY()),AND(ISBLANK($G29)=TRUE,ISBLANK($F29)=FALSE,$F29&lt;TODAY()))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="9" priority="12" stopIfTrue="1">
-      <formula>AND(ISBLANK($D29)=FALSE,ISBLANK($E29)=FALSE,$E29&lt;=TODAY())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B41:C41">
-    <cfRule type="expression" dxfId="8" priority="7" stopIfTrue="1">
-      <formula>ISBLANK($G29)=FALSE</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="7" priority="8" stopIfTrue="1">
-      <formula>OR(AND(ISBLANK($E29)=TRUE,ISBLANK($D29)=FALSE,$D29&lt;=TODAY()),AND(ISBLANK($G29)=TRUE,ISBLANK($F29)=FALSE,$F29&lt;TODAY()))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="6" priority="9" stopIfTrue="1">
-      <formula>AND(ISBLANK($D29)=FALSE,ISBLANK($E29)=FALSE,$E29&lt;=TODAY())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B41:C41">
-    <cfRule type="expression" dxfId="5" priority="4" stopIfTrue="1">
-      <formula>ISBLANK($G29)=FALSE</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="5" stopIfTrue="1">
-      <formula>OR(AND(ISBLANK($E29)=TRUE,ISBLANK($D29)=FALSE,$D29&lt;=TODAY()),AND(ISBLANK($G29)=TRUE,ISBLANK($F29)=FALSE,$F29&lt;TODAY()))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="3" priority="6" stopIfTrue="1">
-      <formula>AND(ISBLANK($D29)=FALSE,ISBLANK($E29)=FALSE,$E29&lt;=TODAY())</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B41:C41">
-    <cfRule type="expression" dxfId="2" priority="1" stopIfTrue="1">
-      <formula>ISBLANK($G29)=FALSE</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2" stopIfTrue="1">
-      <formula>OR(AND(ISBLANK($E29)=TRUE,ISBLANK($D29)=FALSE,$D29&lt;=TODAY()),AND(ISBLANK($G29)=TRUE,ISBLANK($F29)=FALSE,$F29&lt;TODAY()))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="3" stopIfTrue="1">
-      <formula>AND(ISBLANK($D29)=FALSE,ISBLANK($E29)=FALSE,$E29&lt;=TODAY())</formula>
+    <cfRule type="expression" dxfId="0" priority="723" stopIfTrue="1">
+      <formula>OR(AND($D7&gt;=H$4,$D7&lt;=H$4+$K$2-1),AND($F7&gt;=H$4,$F7&lt;=H$4+$K$2-1),AND($D7&lt;H$4,$F7&gt;H$4+$K$2-1))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations disablePrompts="1" count="2">

--- a/01_企画/【ガント】PAW！.xlsx
+++ b/01_企画/【ガント】PAW！.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\suire\OneDrive\デスクトップ\【就職作品】PAW！\00_Git\01_企画\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1806B4F7-40A1-4288-875F-99C8E36F5D3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA09B9E3-8124-4166-9975-829BB1F1EF0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="スケジュール" sheetId="7" r:id="rId1"/>
@@ -14943,7 +14943,9 @@
       <c r="F24" s="17">
         <v>46297</v>
       </c>
-      <c r="G24" s="17"/>
+      <c r="G24" s="17">
+        <v>46299</v>
+      </c>
       <c r="H24" s="18" t="str">
         <f t="shared" ca="1" si="32"/>
         <v/>
@@ -15026,7 +15028,7 @@
       </c>
       <c r="AB24" s="18" t="str">
         <f t="shared" ca="1" si="34"/>
-        <v/>
+        <v>→</v>
       </c>
       <c r="AC24" s="18" t="str">
         <f t="shared" ca="1" si="34"/>
@@ -57576,18 +57578,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_x5b9f__x88c5_ xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">false</_x5b9f__x88c5_>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100A6A6C361903FA540AF4D79E6EA2B777C" ma:contentTypeVersion="20" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="c51e6dc635d7884d0c2c325f025ec4a5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="aaa52e1c-8772-4366-aa63-bf636c80ebd4" xmlns:ns3="0c73c1f5-50cd-4477-a315-44bef7b8a847" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="946a030821db90bf783b20c6c950d067" ns2:_="" ns3:_="">
     <xsd:import namespace="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
@@ -57854,6 +57844,18 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_x5b9f__x88c5_ xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">false</_x5b9f__x88c5_>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -57864,17 +57866,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27817FF2-F49B-48C7-B495-DA609CB0DD24}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="0c73c1f5-50cd-4477-a315-44bef7b8a847"/>
-    <ds:schemaRef ds:uri="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA8FA761-269E-4D58-A147-A218C33C175C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -57893,6 +57884,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27817FF2-F49B-48C7-B495-DA609CB0DD24}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="0c73c1f5-50cd-4477-a315-44bef7b8a847"/>
+    <ds:schemaRef ds:uri="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B48DB0D-B5D1-462E-89C6-32857537C424}">
   <ds:schemaRefs>

--- a/01_企画/【ガント】PAW！.xlsx
+++ b/01_企画/【ガント】PAW！.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\suire\OneDrive\デスクトップ\【就職作品】PAW！\00_Git\01_企画\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA09B9E3-8124-4166-9975-829BB1F1EF0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04247659-98A2-4A9F-9904-926BF6069B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="スケジュール" sheetId="7" r:id="rId1"/>
@@ -15496,7 +15496,9 @@
       <c r="F25" s="17">
         <v>46301</v>
       </c>
-      <c r="G25" s="17"/>
+      <c r="G25" s="17">
+        <v>46299</v>
+      </c>
       <c r="H25" s="18" t="str">
         <f t="shared" ca="1" si="32"/>
         <v/>
@@ -15579,7 +15581,7 @@
       </c>
       <c r="AB25" s="18" t="str">
         <f t="shared" ca="1" si="34"/>
-        <v/>
+        <v>→</v>
       </c>
       <c r="AC25" s="18" t="str">
         <f t="shared" ca="1" si="34"/>
@@ -57578,6 +57580,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_x5b9f__x88c5_ xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">false</_x5b9f__x88c5_>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100A6A6C361903FA540AF4D79E6EA2B777C" ma:contentTypeVersion="20" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="c51e6dc635d7884d0c2c325f025ec4a5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="aaa52e1c-8772-4366-aa63-bf636c80ebd4" xmlns:ns3="0c73c1f5-50cd-4477-a315-44bef7b8a847" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="946a030821db90bf783b20c6c950d067" ns2:_="" ns3:_="">
     <xsd:import namespace="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
@@ -57844,18 +57858,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_x5b9f__x88c5_ xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">false</_x5b9f__x88c5_>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -57866,6 +57868,17 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27817FF2-F49B-48C7-B495-DA609CB0DD24}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="0c73c1f5-50cd-4477-a315-44bef7b8a847"/>
+    <ds:schemaRef ds:uri="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA8FA761-269E-4D58-A147-A218C33C175C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -57884,17 +57897,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27817FF2-F49B-48C7-B495-DA609CB0DD24}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="0c73c1f5-50cd-4477-a315-44bef7b8a847"/>
-    <ds:schemaRef ds:uri="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B48DB0D-B5D1-462E-89C6-32857537C424}">
   <ds:schemaRefs>

--- a/01_企画/【ガント】PAW！.xlsx
+++ b/01_企画/【ガント】PAW！.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\suire\OneDrive\デスクトップ\【就職作品】PAW！\00_Git\01_企画\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2416009\Project\PAW\01_企画\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04247659-98A2-4A9F-9904-926BF6069B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55E57A04-DAB6-4DF1-A32D-D48E3CE7D434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,6 +39,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -16049,7 +16052,9 @@
       <c r="F26" s="17">
         <v>46303</v>
       </c>
-      <c r="G26" s="17"/>
+      <c r="G26" s="17">
+        <v>46303</v>
+      </c>
       <c r="H26" s="18" t="str">
         <f t="shared" ca="1" si="32"/>
         <v/>
@@ -16148,7 +16153,7 @@
       </c>
       <c r="AF26" s="18" t="str">
         <f t="shared" ca="1" si="34"/>
-        <v/>
+        <v>→</v>
       </c>
       <c r="AG26" s="18" t="str">
         <f t="shared" ca="1" si="34"/>
@@ -57580,15 +57585,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_x5b9f__x88c5_ xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">false</_x5b9f__x88c5_>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -57859,21 +57861,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_x5b9f__x88c5_ xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">false</_x5b9f__x88c5_>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27817FF2-F49B-48C7-B495-DA609CB0DD24}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B48DB0D-B5D1-462E-89C6-32857537C424}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="0c73c1f5-50cd-4477-a315-44bef7b8a847"/>
-    <ds:schemaRef ds:uri="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -57898,9 +57900,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B48DB0D-B5D1-462E-89C6-32857537C424}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27817FF2-F49B-48C7-B495-DA609CB0DD24}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="0c73c1f5-50cd-4477-a315-44bef7b8a847"/>
+    <ds:schemaRef ds:uri="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/01_企画/【ガント】PAW！.xlsx
+++ b/01_企画/【ガント】PAW！.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2416009\Project\PAW\01_企画\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55E57A04-DAB6-4DF1-A32D-D48E3CE7D434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6F4FC36-EA0D-4D3D-8122-B05EB2CB2258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16605,7 +16605,9 @@
       <c r="F27" s="17">
         <v>46308</v>
       </c>
-      <c r="G27" s="17"/>
+      <c r="G27" s="17">
+        <v>46312</v>
+      </c>
       <c r="H27" s="18" t="str">
         <f t="shared" ca="1" si="32"/>
         <v/>
@@ -17697,7 +17699,9 @@
       <c r="F29" s="17">
         <v>46310</v>
       </c>
-      <c r="G29" s="17"/>
+      <c r="G29" s="17">
+        <v>46312</v>
+      </c>
       <c r="H29" s="18" t="str">
         <f t="shared" ca="1" si="32"/>
         <v/>
@@ -57585,12 +57589,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_x5b9f__x88c5_ xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">false</_x5b9f__x88c5_>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -57861,21 +57868,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_x5b9f__x88c5_ xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">false</_x5b9f__x88c5_>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B48DB0D-B5D1-462E-89C6-32857537C424}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27817FF2-F49B-48C7-B495-DA609CB0DD24}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="0c73c1f5-50cd-4477-a315-44bef7b8a847"/>
+    <ds:schemaRef ds:uri="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -57900,12 +57907,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27817FF2-F49B-48C7-B495-DA609CB0DD24}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B48DB0D-B5D1-462E-89C6-32857537C424}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="0c73c1f5-50cd-4477-a315-44bef7b8a847"/>
-    <ds:schemaRef ds:uri="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/01_企画/【ガント】PAW！.xlsx
+++ b/01_企画/【ガント】PAW！.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2416009\Project\PAW\01_企画\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6F4FC36-EA0D-4D3D-8122-B05EB2CB2258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63E0F41B-75F0-4742-A288-1FDDCD5719BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1200" yWindow="2295" windowWidth="19605" windowHeight="12615" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="スケジュール" sheetId="7" r:id="rId1"/>
@@ -19344,7 +19344,9 @@
       <c r="F32" s="17">
         <v>46314</v>
       </c>
-      <c r="G32" s="17"/>
+      <c r="G32" s="17">
+        <v>46315</v>
+      </c>
       <c r="H32" s="18" t="str">
         <f t="shared" ca="1" si="32"/>
         <v/>
@@ -57589,15 +57591,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_x5b9f__x88c5_ xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">false</_x5b9f__x88c5_>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -57868,21 +57867,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_x5b9f__x88c5_ xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">false</_x5b9f__x88c5_>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27817FF2-F49B-48C7-B495-DA609CB0DD24}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B48DB0D-B5D1-462E-89C6-32857537C424}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="0c73c1f5-50cd-4477-a315-44bef7b8a847"/>
-    <ds:schemaRef ds:uri="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -57907,9 +57906,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B48DB0D-B5D1-462E-89C6-32857537C424}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27817FF2-F49B-48C7-B495-DA609CB0DD24}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="0c73c1f5-50cd-4477-a315-44bef7b8a847"/>
+    <ds:schemaRef ds:uri="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>